--- a/public/templates/office/Phase5_데이터이관_정합성_대사표.xlsx
+++ b/public/templates/office/Phase5_데이터이관_정합성_대사표.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터이관_정합성대사" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_데이터이관_정합성대사" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +30,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +47,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +66,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,27 +116,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,49 +528,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>데이터이관_정합성대사</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>[EMP-XLS-P5-02] 초기 마스터 및 레거시 데이터 이관 정합성 대사표 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>ProductLab 전성분 마스터, 법령·가이드라인 RAG 벡터, 100대 규제 룰셋 및 임직원 권한 이관 100% 대사 검증 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>테이블 구분</t>
+          <t>이관 그룹</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>원천 테이블 (Source)</t>
+          <t>원천 시스템 / 테이블 (Source)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>대상 테이블 (Target)</t>
+          <t>대상 테이블 (SyncGuard AI PRD)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -534,12 +579,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>대상 건수 (B)</t>
+          <t>이관 건수 (B)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>불일치 건수 (A-B)</t>
+          <t>오차 (A-B)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -549,258 +594,340 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>금액 및 무결성 대사 결과</t>
+          <t>체크섬·무결성 검증 결과</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>검증 판정</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>최종 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>TB_USER_MST</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>sys_user</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>124530</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>124530</v>
-      </c>
-      <c r="F5" s="4">
+          <t>임직원·권한</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>HB-SSO 인사뷰 (V_HB_EMP_AUTH)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>tb_sys_user / tb_user_role</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>4820</v>
+      </c>
+      <c r="F5" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="7">
         <f>E5/D5*100</f>
         <v/>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>상태값 및 암호화 100% 일치</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>부서코드 및 역할(심의관/마케터/관리자) 100% 일치</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>적격</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>권한/메뉴</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>TB_AUTH_GRP</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>sys_role_permission</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>3420</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>3420</v>
-      </c>
-      <c r="F6" s="6">
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>공통코드·용어</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>표준코드마스터 (EMP_DEG_070)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>tb_cmn_grp_cd / tb_cmn_dtl_cd</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>385</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>385</v>
+      </c>
+      <c r="F6" s="11">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="11">
         <f>E6/D6*100</f>
         <v/>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>역할 매핑 무결성 100% 일치</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>32개 코드그룹 및 353개 상세코드 무결성 일치</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>적격</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>상품마스터</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>TB_PROD_INFO</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>domain_product</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>48210</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>48210</v>
-      </c>
-      <c r="F7" s="4">
+          <t>전성분 마스터</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ProductLab 뷰 (V_AI_INGREDIENT_SPEC)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>tb_ingredient_mst</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>28450</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>28450</v>
+      </c>
+      <c r="F7" s="7">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="7">
         <f>E7/D7*100</f>
         <v/>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>카테고리 및 가격 정보 100% 일치</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CAS 번호, 국문/영문 INCI명, 배합한도 수치 오차 0건</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>적격</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>거래/주문</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>TB_ORDER_HIST</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>domain_order</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1892400</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>1892400</v>
-      </c>
-      <c r="F8" s="6">
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>제품·처방 매핑</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ProductLab 제품뷰 (V_AI_PRODUCT_BOM)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>tb_product_ingredient_map</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>142600</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>142600</v>
+      </c>
+      <c r="F8" s="11">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="11">
         <f>E8/D8*100</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>총 누적 결제금액 오차 0원 일치</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>브랜드(루미에르·벨르코어 등) 4,200개 품목 매핑 일치</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>적격</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>첨부파일</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>TB_FILE_UPLOAD</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>oss_file_meta</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>87600</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>87600</v>
-      </c>
-      <c r="F9" s="4">
+          <t>규제 룰셋 사전</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>컴플라이언스 사전 (EMP_EXE_010)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>tb_compliance_rule</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F9" s="7">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="7">
         <f>E9/D9*100</f>
         <v/>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>SHA256 해시 검증 100% 통과</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>국문 100대 룰셋 + 영문 20대(CR-2026-003) 정규식 검증 완료</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>적격</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>RAG 벡터 지식</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>식약처 고시·가이드라인·판례 청크</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>tb_rag_document_chunk (pgvector)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>48500</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>48500</v>
+      </c>
+      <c r="F10" s="11">
+        <f>D10-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>E10/D10*100</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>1536차원 벡터 임베딩 Null 0건, HNSW 인덱스 빌드 완료</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>골든셋 기준표</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>표준 평가 골든셋 (EMP_TST_050)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>tb_golden_test_case</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" s="7">
+        <f>D11-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>E11/D11*100</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>기본 50문항 + 감리 보강 8문항 정답 레이블 100% 일치</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>총 5개 핵심 테이블</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>총 5개 대상 테이블</t>
-        </is>
-      </c>
-      <c r="D10" s="6">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>SUM(E5:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>SUM(F5:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>E10/D10*100</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>데이터 정합성 100.0% 검증 완료</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>총 7개 핵심 데이터 그룹</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>상용 DB(RDS PostgreSQL 16 PRD) 이관 총계</t>
+        </is>
+      </c>
+      <c r="D12" s="15">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="15">
+        <f>E12/D12*100</f>
+        <v/>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>총 224,933건 오차 0건 (100.0% 일치 확인)</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>최종 합격</t>
         </is>
@@ -808,8 +935,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/office/Phase5_데이터이관_정합성_대사표.xlsx
+++ b/public/templates/office/Phase5_데이터이관_정합성_대사표.xlsx
@@ -545,14 +545,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P5-02] 초기 마스터 및 레거시 데이터 이관 정합성 대사표 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P5-02] 초기 마스터 및 레거시 데이터 이관 정합성 대사표 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 마스터, 법령·가이드라인 RAG 벡터, 100대 규제 룰셋 및 임직원 권한 이관 100% 대사 검증 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>PLM-Nexus 자재BOM 마스터, 법령·가이드라인 RAG 벡터, 100대 규제 룰셋 및 임직원 권한 이관 100% 대사 검증 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>대상 테이블 (SyncGuard AI PRD)</t>
+          <t>대상 테이블 (SyncFlow AI PRD)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>부서코드 및 역할(심의관/마케터/관리자) 100% 일치</t>
+          <t>부서코드 및 역할(검토위원/구매담당자/관리자) 100% 일치</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>전성분 마스터</t>
+          <t>자재BOM 마스터</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ProductLab 뷰 (V_AI_INGREDIENT_SPEC)</t>
+          <t>PLM-Nexus 뷰 (V_AI_INGREDIENT_SPEC)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>CAS 번호, 국문/영문 INCI명, 배합한도 수치 오차 0건</t>
+          <t>CAS 번호, 국문/영문 CAS/RoHS명, 유해물질한도 수치 오차 0건</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -729,12 +729,12 @@
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>제품·처방 매핑</t>
+          <t>제품·설계사양 매핑</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>ProductLab 제품뷰 (V_AI_PRODUCT_BOM)</t>
+          <t>PLM-Nexus 제품뷰 (V_AI_PRODUCT_BOM)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>브랜드(루미에르·벨르코어 등) 4,200개 품목 매핑 일치</t>
+          <t>사업본부(전장시스템·배터리모듈 등) 4,200개 품목 매핑 일치</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>식약처 고시·가이드라인·판례 청크</t>
+          <t>공정위·표준원 고시·가이드라인·판례 청크</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
